--- a/XLSX/Player.xlsx
+++ b/XLSX/Player.xlsx
@@ -1,16 +1,16 @@
 
 <file path=xl/workbook.xml><?xml version="1.0" encoding="utf-8"?>
 <workbook xmlns="http://schemas.openxmlformats.org/spreadsheetml/2006/main" xmlns:r="http://schemas.openxmlformats.org/officeDocument/2006/relationships" xmlns:mc="http://schemas.openxmlformats.org/markup-compatibility/2006" xmlns:x15="http://schemas.microsoft.com/office/spreadsheetml/2010/11/main" xmlns:xr="http://schemas.microsoft.com/office/spreadsheetml/2014/revision" xmlns:xr6="http://schemas.microsoft.com/office/spreadsheetml/2016/revision6" xmlns:xr10="http://schemas.microsoft.com/office/spreadsheetml/2016/revision10" xmlns:xr2="http://schemas.microsoft.com/office/spreadsheetml/2015/revision2" mc:Ignorable="x15 xr xr6 xr10 xr2">
-  <fileVersion appName="xl" lastEdited="7" lowestEdited="6" rupBuild="29725"/>
+  <fileVersion appName="xl" lastEdited="7" lowestEdited="6" rupBuild="29822"/>
   <workbookPr/>
   <mc:AlternateContent xmlns:mc="http://schemas.openxmlformats.org/markup-compatibility/2006">
     <mc:Choice Requires="x15">
-      <x15ac:absPath xmlns:x15ac="http://schemas.microsoft.com/office/spreadsheetml/2010/11/ac" url="D:\Work\dodge-ball\XLSX\"/>
+      <x15ac:absPath xmlns:x15ac="http://schemas.microsoft.com/office/spreadsheetml/2010/11/ac" url="D:\Works\dodge-ball\XLSX\"/>
     </mc:Choice>
   </mc:AlternateContent>
-  <xr:revisionPtr revIDLastSave="0" documentId="13_ncr:1_{3A1AA0EC-206B-4CB7-83B0-798B78015EEE}" xr6:coauthVersionLast="47" xr6:coauthVersionMax="47" xr10:uidLastSave="{00000000-0000-0000-0000-000000000000}"/>
+  <xr:revisionPtr revIDLastSave="0" documentId="13_ncr:1_{C8ADC191-372D-4EC2-AF7D-0A835BA3A9BA}" xr6:coauthVersionLast="47" xr6:coauthVersionMax="47" xr10:uidLastSave="{00000000-0000-0000-0000-000000000000}"/>
   <bookViews>
-    <workbookView xWindow="-108" yWindow="-108" windowWidth="30936" windowHeight="16776" xr2:uid="{00000000-000D-0000-FFFF-FFFF00000000}"/>
+    <workbookView xWindow="28680" yWindow="-120" windowWidth="29040" windowHeight="15720" xr2:uid="{00000000-000D-0000-FFFF-FFFF00000000}"/>
   </bookViews>
   <sheets>
     <sheet name="+Player" sheetId="1" r:id="rId1"/>
@@ -25,7 +25,7 @@
 </file>
 
 <file path=xl/sharedStrings.xml><?xml version="1.0" encoding="utf-8"?>
-<sst xmlns="http://schemas.openxmlformats.org/spreadsheetml/2006/main" count="4" uniqueCount="3">
+<sst xmlns="http://schemas.openxmlformats.org/spreadsheetml/2006/main" count="6" uniqueCount="4">
   <si>
     <t>Level</t>
     <phoneticPr fontId="3" type="noConversion"/>
@@ -36,6 +36,10 @@
   </si>
   <si>
     <t>int</t>
+    <phoneticPr fontId="3" type="noConversion"/>
+  </si>
+  <si>
+    <t>LevelUpTime</t>
     <phoneticPr fontId="3" type="noConversion"/>
   </si>
 </sst>
@@ -397,108 +401,144 @@
 
 <file path=xl/worksheets/sheet1.xml><?xml version="1.0" encoding="utf-8"?>
 <worksheet xmlns="http://schemas.openxmlformats.org/spreadsheetml/2006/main" xmlns:r="http://schemas.openxmlformats.org/officeDocument/2006/relationships" xmlns:mc="http://schemas.openxmlformats.org/markup-compatibility/2006" xmlns:x14ac="http://schemas.microsoft.com/office/spreadsheetml/2009/9/ac" xmlns:xr="http://schemas.microsoft.com/office/spreadsheetml/2014/revision" xmlns:xr2="http://schemas.microsoft.com/office/spreadsheetml/2015/revision2" xmlns:xr3="http://schemas.microsoft.com/office/spreadsheetml/2016/revision3" mc:Ignorable="x14ac xr xr2 xr3" xr:uid="{00000000-0001-0000-0000-000000000000}">
-  <dimension ref="A1:B12"/>
-  <sheetFormatPr defaultRowHeight="17.399999999999999" x14ac:dyDescent="0.4"/>
+  <dimension ref="A1:C12"/>
+  <sheetFormatPr defaultRowHeight="16.5" x14ac:dyDescent="0.3"/>
   <cols>
-    <col min="1" max="1" width="23.59765625" customWidth="1"/>
-    <col min="2" max="2" width="25.19921875" customWidth="1"/>
-    <col min="3" max="3" width="22.19921875" customWidth="1"/>
+    <col min="1" max="1" width="23.625" customWidth="1"/>
+    <col min="2" max="2" width="25.25" customWidth="1"/>
+    <col min="3" max="3" width="22.25" customWidth="1"/>
   </cols>
   <sheetData>
-    <row r="1" spans="1:2" s="1" customFormat="1" x14ac:dyDescent="0.4">
+    <row r="1" spans="1:3" s="1" customFormat="1" x14ac:dyDescent="0.3">
       <c r="A1" s="1" t="s">
         <v>0</v>
       </c>
       <c r="B1" s="1" t="s">
         <v>1</v>
       </c>
-    </row>
-    <row r="2" spans="1:2" s="2" customFormat="1" x14ac:dyDescent="0.4">
+      <c r="C1" s="1" t="s">
+        <v>3</v>
+      </c>
+    </row>
+    <row r="2" spans="1:3" s="2" customFormat="1" x14ac:dyDescent="0.3">
       <c r="A2" s="2" t="s">
         <v>2</v>
       </c>
       <c r="B2" s="2" t="s">
         <v>2</v>
       </c>
-    </row>
-    <row r="3" spans="1:2" x14ac:dyDescent="0.4">
+      <c r="C2" s="2" t="s">
+        <v>2</v>
+      </c>
+    </row>
+    <row r="3" spans="1:3" x14ac:dyDescent="0.3">
       <c r="A3">
         <v>1</v>
       </c>
       <c r="B3">
         <v>100</v>
       </c>
-    </row>
-    <row r="4" spans="1:2" x14ac:dyDescent="0.4">
+      <c r="C3">
+        <v>0</v>
+      </c>
+    </row>
+    <row r="4" spans="1:3" x14ac:dyDescent="0.3">
       <c r="A4">
         <v>2</v>
       </c>
       <c r="B4">
         <v>200</v>
       </c>
-    </row>
-    <row r="5" spans="1:2" x14ac:dyDescent="0.4">
+      <c r="C4">
+        <v>30</v>
+      </c>
+    </row>
+    <row r="5" spans="1:3" x14ac:dyDescent="0.3">
       <c r="A5">
         <v>3</v>
       </c>
       <c r="B5">
         <v>300</v>
       </c>
-    </row>
-    <row r="6" spans="1:2" x14ac:dyDescent="0.4">
+      <c r="C5">
+        <v>60</v>
+      </c>
+    </row>
+    <row r="6" spans="1:3" x14ac:dyDescent="0.3">
       <c r="A6">
         <v>4</v>
       </c>
       <c r="B6">
         <v>400</v>
       </c>
-    </row>
-    <row r="7" spans="1:2" x14ac:dyDescent="0.4">
+      <c r="C6">
+        <v>90</v>
+      </c>
+    </row>
+    <row r="7" spans="1:3" x14ac:dyDescent="0.3">
       <c r="A7">
         <v>5</v>
       </c>
       <c r="B7">
         <v>500</v>
       </c>
-    </row>
-    <row r="8" spans="1:2" x14ac:dyDescent="0.4">
+      <c r="C7">
+        <v>120</v>
+      </c>
+    </row>
+    <row r="8" spans="1:3" x14ac:dyDescent="0.3">
       <c r="A8">
         <v>6</v>
       </c>
       <c r="B8">
         <v>600</v>
       </c>
-    </row>
-    <row r="9" spans="1:2" x14ac:dyDescent="0.4">
+      <c r="C8">
+        <v>150</v>
+      </c>
+    </row>
+    <row r="9" spans="1:3" x14ac:dyDescent="0.3">
       <c r="A9">
         <v>7</v>
       </c>
       <c r="B9">
         <v>700</v>
       </c>
-    </row>
-    <row r="10" spans="1:2" x14ac:dyDescent="0.4">
+      <c r="C9">
+        <v>180</v>
+      </c>
+    </row>
+    <row r="10" spans="1:3" x14ac:dyDescent="0.3">
       <c r="A10">
         <v>8</v>
       </c>
       <c r="B10">
         <v>800</v>
       </c>
-    </row>
-    <row r="11" spans="1:2" x14ac:dyDescent="0.4">
+      <c r="C10">
+        <v>210</v>
+      </c>
+    </row>
+    <row r="11" spans="1:3" x14ac:dyDescent="0.3">
       <c r="A11">
         <v>9</v>
       </c>
       <c r="B11">
         <v>900</v>
       </c>
-    </row>
-    <row r="12" spans="1:2" x14ac:dyDescent="0.4">
+      <c r="C11">
+        <v>240</v>
+      </c>
+    </row>
+    <row r="12" spans="1:3" x14ac:dyDescent="0.3">
       <c r="A12">
         <v>10</v>
       </c>
       <c r="B12">
         <v>1000</v>
+      </c>
+      <c r="C12">
+        <v>270</v>
       </c>
     </row>
   </sheetData>

--- a/XLSX/Player.xlsx
+++ b/XLSX/Player.xlsx
@@ -8,7 +8,7 @@
       <x15ac:absPath xmlns:x15ac="http://schemas.microsoft.com/office/spreadsheetml/2010/11/ac" url="D:\Works\dodge-ball\XLSX\"/>
     </mc:Choice>
   </mc:AlternateContent>
-  <xr:revisionPtr revIDLastSave="0" documentId="13_ncr:1_{C8ADC191-372D-4EC2-AF7D-0A835BA3A9BA}" xr6:coauthVersionLast="47" xr6:coauthVersionMax="47" xr10:uidLastSave="{00000000-0000-0000-0000-000000000000}"/>
+  <xr:revisionPtr revIDLastSave="0" documentId="13_ncr:1_{01B701BE-A73C-4181-87A2-BE446537765B}" xr6:coauthVersionLast="47" xr6:coauthVersionMax="47" xr10:uidLastSave="{00000000-0000-0000-0000-000000000000}"/>
   <bookViews>
     <workbookView xWindow="28680" yWindow="-120" windowWidth="29040" windowHeight="15720" xr2:uid="{00000000-000D-0000-FFFF-FFFF00000000}"/>
   </bookViews>
@@ -450,7 +450,7 @@
         <v>200</v>
       </c>
       <c r="C4">
-        <v>30</v>
+        <v>10</v>
       </c>
     </row>
     <row r="5" spans="1:3" x14ac:dyDescent="0.3">
@@ -461,7 +461,7 @@
         <v>300</v>
       </c>
       <c r="C5">
-        <v>60</v>
+        <v>20</v>
       </c>
     </row>
     <row r="6" spans="1:3" x14ac:dyDescent="0.3">
@@ -472,7 +472,7 @@
         <v>400</v>
       </c>
       <c r="C6">
-        <v>90</v>
+        <v>30</v>
       </c>
     </row>
     <row r="7" spans="1:3" x14ac:dyDescent="0.3">
@@ -483,7 +483,7 @@
         <v>500</v>
       </c>
       <c r="C7">
-        <v>120</v>
+        <v>40</v>
       </c>
     </row>
     <row r="8" spans="1:3" x14ac:dyDescent="0.3">
@@ -494,7 +494,7 @@
         <v>600</v>
       </c>
       <c r="C8">
-        <v>150</v>
+        <v>50</v>
       </c>
     </row>
     <row r="9" spans="1:3" x14ac:dyDescent="0.3">
@@ -505,7 +505,7 @@
         <v>700</v>
       </c>
       <c r="C9">
-        <v>180</v>
+        <v>60</v>
       </c>
     </row>
     <row r="10" spans="1:3" x14ac:dyDescent="0.3">
@@ -516,7 +516,7 @@
         <v>800</v>
       </c>
       <c r="C10">
-        <v>210</v>
+        <v>70</v>
       </c>
     </row>
     <row r="11" spans="1:3" x14ac:dyDescent="0.3">
@@ -527,7 +527,7 @@
         <v>900</v>
       </c>
       <c r="C11">
-        <v>240</v>
+        <v>80</v>
       </c>
     </row>
     <row r="12" spans="1:3" x14ac:dyDescent="0.3">
@@ -538,7 +538,7 @@
         <v>1000</v>
       </c>
       <c r="C12">
-        <v>270</v>
+        <v>90</v>
       </c>
     </row>
   </sheetData>

--- a/XLSX/Player.xlsx
+++ b/XLSX/Player.xlsx
@@ -8,7 +8,7 @@
       <x15ac:absPath xmlns:x15ac="http://schemas.microsoft.com/office/spreadsheetml/2010/11/ac" url="D:\Works\dodge-ball\XLSX\"/>
     </mc:Choice>
   </mc:AlternateContent>
-  <xr:revisionPtr revIDLastSave="0" documentId="13_ncr:1_{01B701BE-A73C-4181-87A2-BE446537765B}" xr6:coauthVersionLast="47" xr6:coauthVersionMax="47" xr10:uidLastSave="{00000000-0000-0000-0000-000000000000}"/>
+  <xr:revisionPtr revIDLastSave="0" documentId="13_ncr:1_{E0A66416-4280-48FC-8FF4-C3B55CBF4FD4}" xr6:coauthVersionLast="47" xr6:coauthVersionMax="47" xr10:uidLastSave="{00000000-0000-0000-0000-000000000000}"/>
   <bookViews>
     <workbookView xWindow="28680" yWindow="-120" windowWidth="29040" windowHeight="15720" xr2:uid="{00000000-000D-0000-FFFF-FFFF00000000}"/>
   </bookViews>
@@ -25,7 +25,7 @@
 </file>
 
 <file path=xl/sharedStrings.xml><?xml version="1.0" encoding="utf-8"?>
-<sst xmlns="http://schemas.openxmlformats.org/spreadsheetml/2006/main" count="6" uniqueCount="4">
+<sst xmlns="http://schemas.openxmlformats.org/spreadsheetml/2006/main" count="8" uniqueCount="6">
   <si>
     <t>Level</t>
     <phoneticPr fontId="3" type="noConversion"/>
@@ -40,6 +40,14 @@
   </si>
   <si>
     <t>LevelUpTime</t>
+    <phoneticPr fontId="3" type="noConversion"/>
+  </si>
+  <si>
+    <t>EnemySpawnTime</t>
+    <phoneticPr fontId="3" type="noConversion"/>
+  </si>
+  <si>
+    <t>float</t>
     <phoneticPr fontId="3" type="noConversion"/>
   </si>
 </sst>
@@ -401,15 +409,16 @@
 
 <file path=xl/worksheets/sheet1.xml><?xml version="1.0" encoding="utf-8"?>
 <worksheet xmlns="http://schemas.openxmlformats.org/spreadsheetml/2006/main" xmlns:r="http://schemas.openxmlformats.org/officeDocument/2006/relationships" xmlns:mc="http://schemas.openxmlformats.org/markup-compatibility/2006" xmlns:x14ac="http://schemas.microsoft.com/office/spreadsheetml/2009/9/ac" xmlns:xr="http://schemas.microsoft.com/office/spreadsheetml/2014/revision" xmlns:xr2="http://schemas.microsoft.com/office/spreadsheetml/2015/revision2" xmlns:xr3="http://schemas.microsoft.com/office/spreadsheetml/2016/revision3" mc:Ignorable="x14ac xr xr2 xr3" xr:uid="{00000000-0001-0000-0000-000000000000}">
-  <dimension ref="A1:C12"/>
+  <dimension ref="A1:D12"/>
   <sheetFormatPr defaultRowHeight="16.5" x14ac:dyDescent="0.3"/>
   <cols>
     <col min="1" max="1" width="23.625" customWidth="1"/>
     <col min="2" max="2" width="25.25" customWidth="1"/>
     <col min="3" max="3" width="22.25" customWidth="1"/>
+    <col min="4" max="4" width="30.75" customWidth="1"/>
   </cols>
   <sheetData>
-    <row r="1" spans="1:3" s="1" customFormat="1" x14ac:dyDescent="0.3">
+    <row r="1" spans="1:4" s="1" customFormat="1" x14ac:dyDescent="0.3">
       <c r="A1" s="1" t="s">
         <v>0</v>
       </c>
@@ -419,8 +428,11 @@
       <c r="C1" s="1" t="s">
         <v>3</v>
       </c>
-    </row>
-    <row r="2" spans="1:3" s="2" customFormat="1" x14ac:dyDescent="0.3">
+      <c r="D1" s="1" t="s">
+        <v>4</v>
+      </c>
+    </row>
+    <row r="2" spans="1:4" s="2" customFormat="1" x14ac:dyDescent="0.3">
       <c r="A2" s="2" t="s">
         <v>2</v>
       </c>
@@ -430,74 +442,95 @@
       <c r="C2" s="2" t="s">
         <v>2</v>
       </c>
-    </row>
-    <row r="3" spans="1:3" x14ac:dyDescent="0.3">
+      <c r="D2" s="2" t="s">
+        <v>5</v>
+      </c>
+    </row>
+    <row r="3" spans="1:4" x14ac:dyDescent="0.3">
       <c r="A3">
         <v>1</v>
       </c>
       <c r="B3">
-        <v>100</v>
+        <v>400</v>
       </c>
       <c r="C3">
         <v>0</v>
       </c>
-    </row>
-    <row r="4" spans="1:3" x14ac:dyDescent="0.3">
+      <c r="D3">
+        <v>3</v>
+      </c>
+    </row>
+    <row r="4" spans="1:4" x14ac:dyDescent="0.3">
       <c r="A4">
         <v>2</v>
       </c>
       <c r="B4">
-        <v>200</v>
+        <v>450</v>
       </c>
       <c r="C4">
         <v>10</v>
       </c>
-    </row>
-    <row r="5" spans="1:3" x14ac:dyDescent="0.3">
+      <c r="D4">
+        <v>2.5</v>
+      </c>
+    </row>
+    <row r="5" spans="1:4" x14ac:dyDescent="0.3">
       <c r="A5">
         <v>3</v>
       </c>
       <c r="B5">
-        <v>300</v>
+        <v>500</v>
       </c>
       <c r="C5">
         <v>20</v>
       </c>
-    </row>
-    <row r="6" spans="1:3" x14ac:dyDescent="0.3">
+      <c r="D5">
+        <v>2</v>
+      </c>
+    </row>
+    <row r="6" spans="1:4" x14ac:dyDescent="0.3">
       <c r="A6">
         <v>4</v>
       </c>
       <c r="B6">
-        <v>400</v>
+        <v>550</v>
       </c>
       <c r="C6">
         <v>30</v>
       </c>
-    </row>
-    <row r="7" spans="1:3" x14ac:dyDescent="0.3">
+      <c r="D6">
+        <v>1.5</v>
+      </c>
+    </row>
+    <row r="7" spans="1:4" x14ac:dyDescent="0.3">
       <c r="A7">
         <v>5</v>
       </c>
       <c r="B7">
-        <v>500</v>
+        <v>600</v>
       </c>
       <c r="C7">
         <v>40</v>
       </c>
-    </row>
-    <row r="8" spans="1:3" x14ac:dyDescent="0.3">
+      <c r="D7">
+        <v>1.4</v>
+      </c>
+    </row>
+    <row r="8" spans="1:4" x14ac:dyDescent="0.3">
       <c r="A8">
         <v>6</v>
       </c>
       <c r="B8">
-        <v>600</v>
+        <v>650</v>
       </c>
       <c r="C8">
         <v>50</v>
       </c>
-    </row>
-    <row r="9" spans="1:3" x14ac:dyDescent="0.3">
+      <c r="D8">
+        <v>1.3</v>
+      </c>
+    </row>
+    <row r="9" spans="1:4" x14ac:dyDescent="0.3">
       <c r="A9">
         <v>7</v>
       </c>
@@ -507,38 +540,50 @@
       <c r="C9">
         <v>60</v>
       </c>
-    </row>
-    <row r="10" spans="1:3" x14ac:dyDescent="0.3">
+      <c r="D9">
+        <v>1.2</v>
+      </c>
+    </row>
+    <row r="10" spans="1:4" x14ac:dyDescent="0.3">
       <c r="A10">
         <v>8</v>
       </c>
       <c r="B10">
-        <v>800</v>
+        <v>750</v>
       </c>
       <c r="C10">
         <v>70</v>
       </c>
-    </row>
-    <row r="11" spans="1:3" x14ac:dyDescent="0.3">
+      <c r="D10">
+        <v>1.1000000000000001</v>
+      </c>
+    </row>
+    <row r="11" spans="1:4" x14ac:dyDescent="0.3">
       <c r="A11">
         <v>9</v>
       </c>
       <c r="B11">
-        <v>900</v>
+        <v>800</v>
       </c>
       <c r="C11">
         <v>80</v>
       </c>
-    </row>
-    <row r="12" spans="1:3" x14ac:dyDescent="0.3">
+      <c r="D11">
+        <v>0.9</v>
+      </c>
+    </row>
+    <row r="12" spans="1:4" x14ac:dyDescent="0.3">
       <c r="A12">
         <v>10</v>
       </c>
       <c r="B12">
-        <v>1000</v>
+        <v>850</v>
       </c>
       <c r="C12">
         <v>90</v>
+      </c>
+      <c r="D12">
+        <v>0.8</v>
       </c>
     </row>
   </sheetData>
